--- a/Experiments_NLP.xlsx
+++ b/Experiments_NLP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://smu-my.sharepoint.com/personal/kh_nguyen_2025_mitb_smu_edu_sg/Documents/Data_Science/SMU/Study/Term 2/CS605 NLP for Smart Assistants/Assignment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{CB199A4B-7D07-4B0C-BB92-4FC6BF07BB6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{910F974C-EBA3-431B-B36A-590DAD57B4A5}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="8_{CB199A4B-7D07-4B0C-BB92-4FC6BF07BB6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C51BEB5-46CB-4D77-AE90-F0D127B5EF90}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{553DC2F9-6C9A-46BB-ABFD-28C82DBA10AE}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="13">
   <si>
     <t>20260611_04_deberta_v3_F1_0.9214</t>
   </si>
@@ -63,6 +63,21 @@
   </si>
   <si>
     <t>20260611_02_kfold_deberta_default_OOF_F1_0.8156</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Cleanlab remove noisy label</t>
+  </si>
+  <si>
+    <t>20260612_02_kfold_deberta_thresh0.55_OOF_F1_0.9103</t>
+  </si>
+  <si>
+    <t>20260612_01_kfold_deberta_default_OOF_F1_0.9094</t>
+  </si>
+  <si>
+    <t>Prompt change, keep all train row, label flip, change weight for low confident</t>
   </si>
 </sst>
 </file>
@@ -70,7 +85,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="0.00000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -103,7 +118,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -438,66 +453,111 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22CC1786-9B20-4260-A956-5D6B7C779879}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="62.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="B2">
+      <c r="C2">
         <v>0.81081000000000003</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
         <v>0</v>
       </c>
-      <c r="B3">
+      <c r="C3">
         <v>0.81281000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
         <v>1</v>
       </c>
-      <c r="B4">
+      <c r="C4">
         <v>0.80066000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
+      <c r="C5">
         <v>0.76112000000000002</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="1">
+      <c r="C6" s="1">
         <v>0.81299999999999994</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
         <v>7</v>
       </c>
-      <c r="B7">
+      <c r="C7">
         <v>0.81238999999999995</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>0.82538999999999996</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9">
+        <v>0.82147999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/Experiments_NLP.xlsx
+++ b/Experiments_NLP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://smu-my.sharepoint.com/personal/kh_nguyen_2025_mitb_smu_edu_sg/Documents/Data_Science/SMU/Study/Term 2/CS605 NLP for Smart Assistants/Assignment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{CB199A4B-7D07-4B0C-BB92-4FC6BF07BB6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C51BEB5-46CB-4D77-AE90-F0D127B5EF90}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="8_{CB199A4B-7D07-4B0C-BB92-4FC6BF07BB6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6DD3FA6-2882-489C-9D99-9E62BE0C318A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{553DC2F9-6C9A-46BB-ABFD-28C82DBA10AE}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="19">
   <si>
     <t>20260611_04_deberta_v3_F1_0.9214</t>
   </si>
@@ -78,6 +78,24 @@
   </si>
   <si>
     <t>Prompt change, keep all train row, label flip, change weight for low confident</t>
+  </si>
+  <si>
+    <t>20260612_09_kfold_deberta_thresh0.56_OOF_F1_0.9099</t>
+  </si>
+  <si>
+    <t>try all threshold 0.5-0.6, 0.01 step</t>
+  </si>
+  <si>
+    <t>20260612_10_kfold_deberta_thresh0.57_OOF_F1_0.9096</t>
+  </si>
+  <si>
+    <t>20260612_11_kfold_deberta_thresh0.58_OOF_F1_0.9092</t>
+  </si>
+  <si>
+    <t>BEST_THRESHOLD = 0.57</t>
+  </si>
+  <si>
+    <t>Note</t>
   </si>
 </sst>
 </file>
@@ -453,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22CC1786-9B20-4260-A956-5D6B7C779879}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="62.21875" bestFit="1" customWidth="1"/>
@@ -461,7 +479,7 @@
     <col min="3" max="3" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -471,8 +489,11 @@
       <c r="C1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -483,7 +504,7 @@
         <v>0.81081000000000003</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -494,7 +515,7 @@
         <v>0.81281000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -505,7 +526,7 @@
         <v>0.80066000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -516,7 +537,7 @@
         <v>0.76112000000000002</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -527,7 +548,7 @@
         <v>0.81299999999999994</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -538,7 +559,7 @@
         <v>0.81238999999999995</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -549,7 +570,7 @@
         <v>0.82538999999999996</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -558,6 +579,42 @@
       </c>
       <c r="C9">
         <v>0.82147999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10">
+        <v>0.82669999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11">
+        <v>0.82801999999999998</v>
+      </c>
+      <c r="D11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12">
+        <v>0.82747000000000004</v>
       </c>
     </row>
   </sheetData>

--- a/Experiments_NLP.xlsx
+++ b/Experiments_NLP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://smu-my.sharepoint.com/personal/kh_nguyen_2025_mitb_smu_edu_sg/Documents/Data_Science/SMU/Study/Term 2/CS605 NLP for Smart Assistants/Assignment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="8_{CB199A4B-7D07-4B0C-BB92-4FC6BF07BB6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6DD3FA6-2882-489C-9D99-9E62BE0C318A}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="8_{CB199A4B-7D07-4B0C-BB92-4FC6BF07BB6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06CB467E-CA4B-4C98-A87A-1E585C7937CF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{553DC2F9-6C9A-46BB-ABFD-28C82DBA10AE}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="22">
   <si>
     <t>20260611_04_deberta_v3_F1_0.9214</t>
   </si>
@@ -96,6 +96,16 @@
   </si>
   <si>
     <t>Note</t>
+  </si>
+  <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>weight = 0.5 if 0.3 &lt;= quality_score &lt; 0.5 else 1.0</t>
+  </si>
+  <si>
+    <t>Run Claude: 26min
+Run Groq: 5 hours</t>
   </si>
 </sst>
 </file>
@@ -134,9 +144,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -152,6 +165,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>212593</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>172899</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0EDDA5B1-F47C-37E7-BC59-8045256F6E89}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3840480"/>
+          <a:ext cx="6133333" cy="3647619"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -471,154 +533,197 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22CC1786-9B20-4260-A956-5D6B7C779879}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="62.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
     <col min="3" max="3" width="10.77734375" customWidth="1"/>
+    <col min="4" max="4" width="62.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>0.81081000000000003</v>
+      </c>
+      <c r="D2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>0.81081000000000003</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3">
+        <v>0.81281000000000003</v>
+      </c>
+      <c r="D3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0.81281000000000003</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>0.80066000000000004</v>
+      </c>
+      <c r="D4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>0.80066000000000004</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>0.76112000000000002</v>
+      </c>
+      <c r="D5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>0.76112000000000002</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0.81299999999999994</v>
+      </c>
+      <c r="D6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="1">
-        <v>0.81299999999999994</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>0.81238999999999995</v>
+      </c>
+      <c r="D7" t="s">
         <v>9</v>
       </c>
-      <c r="B7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7">
-        <v>0.81238999999999995</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>0.82538999999999996</v>
+      </c>
+      <c r="D8" t="s">
         <v>12</v>
       </c>
-      <c r="B8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8">
-        <v>0.82538999999999996</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9">
+        <v>0.82147999999999999</v>
+      </c>
+      <c r="D9" t="s">
         <v>12</v>
       </c>
-      <c r="B9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9">
-        <v>0.82147999999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10">
+        <v>0.82669999999999999</v>
+      </c>
+      <c r="D10" t="s">
         <v>14</v>
       </c>
-      <c r="B10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10">
-        <v>0.82669999999999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11">
+        <v>0.82801999999999998</v>
+      </c>
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" t="s">
         <v>14</v>
       </c>
-      <c r="B11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11">
-        <v>0.82801999999999998</v>
-      </c>
-      <c r="D11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12">
+        <v>0.82747000000000004</v>
+      </c>
+      <c r="D12" t="s">
         <v>14</v>
       </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12">
-        <v>0.82747000000000004</v>
+      <c r="E12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="C13" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Experiments_NLP.xlsx
+++ b/Experiments_NLP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://smu-my.sharepoint.com/personal/kh_nguyen_2025_mitb_smu_edu_sg/Documents/Data_Science/SMU/Study/Term 2/CS605 NLP for Smart Assistants/Assignment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="8_{CB199A4B-7D07-4B0C-BB92-4FC6BF07BB6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06CB467E-CA4B-4C98-A87A-1E585C7937CF}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="8_{CB199A4B-7D07-4B0C-BB92-4FC6BF07BB6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{888442C4-9F67-4E4F-8B24-B33A4CBD43F9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{553DC2F9-6C9A-46BB-ABFD-28C82DBA10AE}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="29">
   <si>
     <t>20260611_04_deberta_v3_F1_0.9214</t>
   </si>
@@ -92,20 +92,40 @@
     <t>20260612_11_kfold_deberta_thresh0.58_OOF_F1_0.9092</t>
   </si>
   <si>
-    <t>BEST_THRESHOLD = 0.57</t>
-  </si>
-  <si>
-    <t>Note</t>
-  </si>
-  <si>
     <t>weight</t>
   </si>
   <si>
     <t>weight = 0.5 if 0.3 &lt;= quality_score &lt; 0.5 else 1.0</t>
   </si>
   <si>
-    <t>Run Claude: 26min
-Run Groq: 5 hours</t>
+    <t>20260613_03_roberta_F1_0.8929</t>
+  </si>
+  <si>
+    <t>20260613_04_deberta_v3_F1_0.9098</t>
+  </si>
+  <si>
+    <t>20260613_02_kfold_deberta_thresh0.57_OOF_F1_0.9144</t>
+  </si>
+  <si>
+    <t>20260613_01_kfold_deberta_default_OOF_F1_0.9127</t>
+  </si>
+  <si>
+    <t>try all threshold 0.5-0.6, 0.01 step, BEST_THRESHOLD = 0.57</t>
+  </si>
+  <si>
+    <t>Run Claude: 26min, Run Groq: 5 hours</t>
+  </si>
+  <si>
+    <t>20260613_02_ensemble_deberta_roberta_default_OOF_F1_0.9085</t>
+  </si>
+  <si>
+    <t>k-fold deberta, k-fold reoberta then ensemble</t>
+  </si>
+  <si>
+    <t>20260613_03_ensemble_deberta_roberta_thresh0.49_OOF_F1_0.9088</t>
+  </si>
+  <si>
+    <t>20260613_04_ensemble_deberta_roberta_thresh0.57_OOF_F1_0.9026</t>
   </si>
 </sst>
 </file>
@@ -173,14 +193,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>212593</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>172899</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>951733</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>43359</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -203,7 +223,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="3840480"/>
+          <a:off x="0" y="4625340"/>
           <a:ext cx="6133333" cy="3647619"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -214,6 +234,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -533,16 +557,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22CC1786-9B20-4260-A956-5D6B7C779879}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="62.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" customWidth="1"/>
-    <col min="3" max="3" width="10.77734375" customWidth="1"/>
-    <col min="4" max="4" width="62.44140625" customWidth="1"/>
+    <col min="3" max="3" width="62.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -550,142 +573,139 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2">
         <v>0.81081000000000003</v>
       </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
       <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3">
         <v>0.81281000000000003</v>
       </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
       <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
       <c r="B4">
         <v>0.80066000000000004</v>
       </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
       <c r="D4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5">
         <v>0.76112000000000002</v>
       </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
       <c r="D5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="1">
         <v>0.81299999999999994</v>
       </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
       <c r="D6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
       <c r="B7">
         <v>0.81238999999999995</v>
       </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
       <c r="D7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>10</v>
       </c>
       <c r="B8">
         <v>0.82538999999999996</v>
       </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
       <c r="D8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
       <c r="B9">
         <v>0.82147999999999999</v>
       </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
       <c r="D9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
       <c r="B10">
         <v>0.82669999999999999</v>
       </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
       <c r="D10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -693,32 +713,112 @@
         <v>0.82801999999999998</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>16</v>
       </c>
       <c r="B12">
         <v>0.82747000000000004</v>
       </c>
+      <c r="C12" t="s">
+        <v>14</v>
+      </c>
       <c r="D12" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>0.81081000000000003</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14">
+        <v>0.79276000000000002</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="C13" s="2" t="s">
+      <c r="B15">
+        <v>0.81747000000000003</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>21</v>
+      </c>
+      <c r="B16">
+        <v>0.81713000000000002</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17">
+        <v>0.81372</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18">
+        <v>0.82025999999999999</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19">
+        <v>0.81818000000000002</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20">
+        <v>0.81322000000000005</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/Experiments_NLP.xlsx
+++ b/Experiments_NLP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://smu-my.sharepoint.com/personal/kh_nguyen_2025_mitb_smu_edu_sg/Documents/Data_Science/SMU/Study/Term 2/CS605 NLP for Smart Assistants/Assignment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="80" documentId="8_{CB199A4B-7D07-4B0C-BB92-4FC6BF07BB6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{888442C4-9F67-4E4F-8B24-B33A4CBD43F9}"/>
+  <xr:revisionPtr revIDLastSave="82" documentId="8_{CB199A4B-7D07-4B0C-BB92-4FC6BF07BB6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82C8A522-88D9-4D7D-92A8-F39295FA92C3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{553DC2F9-6C9A-46BB-ABFD-28C82DBA10AE}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="31">
   <si>
     <t>20260611_04_deberta_v3_F1_0.9214</t>
   </si>
@@ -126,6 +126,12 @@
   </si>
   <si>
     <t>20260613_04_ensemble_deberta_roberta_thresh0.57_OOF_F1_0.9026</t>
+  </si>
+  <si>
+    <t>20260613_13_ensemble_deberta0.7_roberta0.3_thresh0.57_OOF_F1_0.9465</t>
+  </si>
+  <si>
+    <t>ensemble two models</t>
   </si>
 </sst>
 </file>
@@ -234,10 +240,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -557,7 +559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22CC1786-9B20-4260-A956-5D6B7C779879}">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="62.21875" bestFit="1" customWidth="1"/>
@@ -819,6 +821,14 @@
       </c>
       <c r="C20" s="2" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/Experiments_NLP.xlsx
+++ b/Experiments_NLP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://smu-my.sharepoint.com/personal/kh_nguyen_2025_mitb_smu_edu_sg/Documents/Data_Science/SMU/Study/Term 2/CS605 NLP for Smart Assistants/Assignment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="82" documentId="8_{CB199A4B-7D07-4B0C-BB92-4FC6BF07BB6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82C8A522-88D9-4D7D-92A8-F39295FA92C3}"/>
+  <xr:revisionPtr revIDLastSave="91" documentId="8_{CB199A4B-7D07-4B0C-BB92-4FC6BF07BB6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B6E59C8-0EC3-42EE-971A-8D1C0B6E0E00}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{553DC2F9-6C9A-46BB-ABFD-28C82DBA10AE}"/>
+    <workbookView xWindow="936" yWindow="4128" windowWidth="18828" windowHeight="8880" xr2:uid="{553DC2F9-6C9A-46BB-ABFD-28C82DBA10AE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="34">
   <si>
     <t>20260611_04_deberta_v3_F1_0.9214</t>
   </si>
@@ -132,6 +132,15 @@
   </si>
   <si>
     <t>ensemble two models</t>
+  </si>
+  <si>
+    <t>20260613_12_ensemble_deberta0.8_roberta0.2_thresh0.57_OOF_F1_0.9463</t>
+  </si>
+  <si>
+    <t>20260613_14_ensemble_deberta0.6_roberta0.4_thresh0.57_OOF_F1_0.9325</t>
+  </si>
+  <si>
+    <t>20260613_15_ensemble_deberta0.5_roberta0.5_thresh0.57_OOF_F1_0.0000</t>
   </si>
 </sst>
 </file>
@@ -240,6 +249,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -559,7 +572,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22CC1786-9B20-4260-A956-5D6B7C779879}">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="62.21875" bestFit="1" customWidth="1"/>
@@ -827,7 +840,43 @@
       <c r="A21" t="s">
         <v>29</v>
       </c>
+      <c r="B21">
+        <v>0.81269999999999998</v>
+      </c>
       <c r="C21" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22">
+        <v>0.81144000000000005</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23">
+        <v>0.81530000000000002</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24">
+        <v>0.81322000000000005</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>30</v>
       </c>
     </row>

--- a/Experiments_NLP.xlsx
+++ b/Experiments_NLP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://smu-my.sharepoint.com/personal/kh_nguyen_2025_mitb_smu_edu_sg/Documents/Data_Science/SMU/Study/Term 2/CS605 NLP for Smart Assistants/Assignment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="91" documentId="8_{CB199A4B-7D07-4B0C-BB92-4FC6BF07BB6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B6E59C8-0EC3-42EE-971A-8D1C0B6E0E00}"/>
+  <xr:revisionPtr revIDLastSave="102" documentId="8_{CB199A4B-7D07-4B0C-BB92-4FC6BF07BB6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C648559-8312-4C91-B376-10BB789504EA}"/>
   <bookViews>
-    <workbookView xWindow="936" yWindow="4128" windowWidth="18828" windowHeight="8880" xr2:uid="{553DC2F9-6C9A-46BB-ABFD-28C82DBA10AE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{553DC2F9-6C9A-46BB-ABFD-28C82DBA10AE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="38">
   <si>
     <t>20260611_04_deberta_v3_F1_0.9214</t>
   </si>
@@ -141,6 +141,18 @@
   </si>
   <si>
     <t>20260613_15_ensemble_deberta0.5_roberta0.5_thresh0.57_OOF_F1_0.0000</t>
+  </si>
+  <si>
+    <t>20260614_01_multiseed_deberta_10fold_default_OOF_F1_0.9195</t>
+  </si>
+  <si>
+    <t>multiseed (42, 123)</t>
+  </si>
+  <si>
+    <t>20260614_02_multiseed_deberta_10fold_thresh0.5_OOF_F1_0.9195</t>
+  </si>
+  <si>
+    <t>20260614_03_multiseed_deberta_10fold_thresh0.57_OOF_F1_0.9141</t>
   </si>
 </sst>
 </file>
@@ -208,13 +220,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>53340</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>951733</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>43359</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -249,10 +261,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -572,7 +580,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22CC1786-9B20-4260-A956-5D6B7C779879}">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="62.21875" bestFit="1" customWidth="1"/>
@@ -878,6 +886,39 @@
       </c>
       <c r="C24" s="2" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25">
+        <v>0.82050999999999996</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26">
+        <v>0.82050999999999996</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27">
+        <v>0.81238999999999995</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/Experiments_NLP.xlsx
+++ b/Experiments_NLP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://smu-my.sharepoint.com/personal/kh_nguyen_2025_mitb_smu_edu_sg/Documents/Data_Science/SMU/Study/Term 2/CS605 NLP for Smart Assistants/Assignment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="102" documentId="8_{CB199A4B-7D07-4B0C-BB92-4FC6BF07BB6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C648559-8312-4C91-B376-10BB789504EA}"/>
+  <xr:revisionPtr revIDLastSave="105" documentId="8_{CB199A4B-7D07-4B0C-BB92-4FC6BF07BB6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CDA0BA40-2D01-4CE6-B828-A6648159479B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{553DC2F9-6C9A-46BB-ABFD-28C82DBA10AE}"/>
   </bookViews>
@@ -171,12 +171,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -191,10 +197,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -728,17 +738,17 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row r="11" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="3">
         <v>0.82801999999999998</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="3" t="s">
         <v>18</v>
       </c>
     </row>
@@ -811,14 +821,14 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+    <row r="18" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="3">
         <v>0.82025999999999999</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="4" t="s">
         <v>26</v>
       </c>
     </row>
@@ -899,14 +909,14 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+    <row r="26" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="3">
         <v>0.82050999999999996</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="4" t="s">
         <v>35</v>
       </c>
     </row>
